--- a/Table S2.xlsx
+++ b/Table S2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <r>
-      <t xml:space="preserve">Supplementary Methods S2. Unified Cleaning and Standardization Pipeline for the Multi-Source </t>
+      <t xml:space="preserve">Supplementary Table S2. Unified Cleaning and Standardization Pipeline for the Multi-Source </t>
     </r>
     <r>
       <rPr>
@@ -71,7 +71,9 @@
     <t>Extract main text using a unified crawling and parsing framework; remove boilerplate (navigation bars, footers, ads), template noise, and non-informative segments.</t>
   </si>
   <si>
-    <t>• DOM/text-density–based extraction• Noise filtering threshold: low-information paragraphs removed (&lt; X tokens)• Removal of HTML tags and special-symbol artifacts</t>
+    <t>• DOM/text-density–based extraction
+• Noise filtering threshold: low-information paragraphs removed (&lt; X tokens)
+• Removal of HTML tags and special-symbol artifacts</t>
   </si>
   <si>
     <t>Cleaned text; source identifiers (URL/DOI); extraction timestamp</t>
@@ -83,7 +85,9 @@
     <t>Detect and eliminate duplicates or near-duplicates across papers, books, patents, and web sources.</t>
   </si>
   <si>
-    <t>• Text vectorization using SimHash / MinHash• Exact-duplicate threshold: ≥ 0.95 similarity• Near-duplicate threshold: ≥ 0.85 similarity (paragraph level)</t>
+    <t>• Text vectorization using SimHash / MinHash
+• Exact-duplicate threshold: ≥ 0.95 similarity
+• Near-duplicate threshold: ≥ 0.85 similarity (paragraph level)</t>
   </si>
   <si>
     <t>Canonical version retained; duplicate mapping table; similarity scores</t>
@@ -96,7 +100,10 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">• UTF-8 encoding unified• Scientific notation normalized (e.g., 1e6 → 1 × 10⁶)• Standardized units (g/L, CFU/mL, etc.)• Consistent strain naming conventions (e.g., </t>
+      <t xml:space="preserve">• UTF-8 encoding unified
+• Scientific notation normalized (e.g., 1e6 → 1 × 10⁶)
+• Standardized units (g/L, CFU/mL, etc.)
+• Consistent strain naming conventions (e.g., </t>
     </r>
     <r>
       <rPr>
@@ -147,7 +154,8 @@
     <t>Maintain traceability by synchronously updating metadata throughout all processing steps.</t>
   </si>
   <si>
-    <t>• Retained fields: source type, publication year, URL/DOI, crawl date, processing logs• Unique identifier assigned (UUID or hash)</t>
+    <t>• Retained fields: source type, publication year, URL/DOI, crawl date, processing logs
+• Unique identifier assigned (UUID or hash)</t>
   </si>
   <si>
     <t>Structured metadata files (JSON/YAML); index linking text and metadata</t>
@@ -159,7 +167,8 @@
     <t>Assemble the cleaned and standardized content into a domain-specific training corpus.</t>
   </si>
   <si>
-    <t>• Unified segmentation granularity (sentence/paragraph level)• Removal of content not eligible for public release (e.g., copyright-restricted segments)</t>
+    <t>• Unified segmentation granularity (sentence/paragraph level)
+• Removal of content not eligible for public release (e.g., copyright-restricted segments)</t>
   </si>
   <si>
     <t>Final structured corpus ready for model training or downstream tasks</t>
@@ -798,17 +807,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1353,94 +1356,91 @@
   </cols>
   <sheetData>
     <row r="1" ht="57" customHeight="1" spans="1:4">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="38" customHeight="1" spans="1:4">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:4">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:4">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:4">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:4">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:4">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="4" t="s">
         <v>24</v>
       </c>
     </row>
